--- a/data/trans_dic/Predimed_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,6</t>
+          <t>6,94; 14,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 14,01</t>
+          <t>8,14; 14,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,15</t>
+          <t>8,13; 13,07</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 10,74</t>
+          <t>4,39; 10,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,46</t>
+          <t>6,0; 10,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,83</t>
+          <t>5,8; 9,64</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,17; 33,0</t>
+          <t>22,84; 33,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,71; 34,27</t>
+          <t>25,94; 34,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,1; 32,96</t>
+          <t>25,95; 32,28</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,59; 45,41</t>
+          <t>29,78; 44,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,02; 51,55</t>
+          <t>21,58; 51,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,98; 47,2</t>
+          <t>26,26; 47,16</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,91; 27,81</t>
+          <t>17,1; 27,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,25; 36,7</t>
+          <t>27,41; 37,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,04; 30,97</t>
+          <t>23,99; 30,82</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,55; 18,95</t>
+          <t>11,26; 19,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,92; 12,32</t>
+          <t>6,72; 11,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,15; 15,32</t>
+          <t>9,85; 14,83</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,55; 35,5</t>
+          <t>26,8; 35,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,0; 30,76</t>
+          <t>10,19; 30,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,22; 31,16</t>
+          <t>15,95; 31,32</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,32</t>
+          <t>1,05; 4,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,02</t>
+          <t>4,68; 8,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,67</t>
+          <t>2,57; 5,69</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,12; 17,89</t>
+          <t>12,29; 17,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,88; 21,03</t>
+          <t>14,88; 20,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,82; 18,94</t>
+          <t>14,75; 18,82</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21430; 42151</t>
+          <t>21499; 44264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23904; 40513</t>
+          <t>23535; 41003</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49641; 78748</t>
+          <t>48730; 78267</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19736; 47266</t>
+          <t>19303; 46628</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27657; 48076</t>
+          <t>27605; 48508</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52829; 88479</t>
+          <t>52191; 86755</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68006; 96838</t>
+          <t>67022; 97758</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83279; 110991</t>
+          <t>84035; 110674</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161122; 203510</t>
+          <t>160216; 199276</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74227; 110191</t>
+          <t>72260; 108114</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80477; 207234</t>
+          <t>86759; 205641</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>167467; 304274</t>
+          <t>169308; 304004</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29361; 48273</t>
+          <t>29676; 47898</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55465; 74713</t>
+          <t>55806; 75503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90670; 116788</t>
+          <t>90468; 116221</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30835; 50606</t>
+          <t>30081; 51236</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17613; 31380</t>
+          <t>17105; 30463</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52966; 79936</t>
+          <t>51403; 77385</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>155381; 207797</t>
+          <t>156839; 205162</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>74005; 252916</t>
+          <t>83789; 254340</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>242384; 438554</t>
+          <t>224453; 440893</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9317; 39531</t>
+          <t>9589; 39925</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32475; 63759</t>
+          <t>33071; 63370</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>39615; 91972</t>
+          <t>41595; 92141</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>390986; 577176</t>
+          <t>396623; 579041</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>515200; 727904</t>
+          <t>515132; 721511</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>990921; 1266726</t>
+          <t>986434; 1258894</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,28</t>
+          <t>7,53; 14,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,18</t>
+          <t>7,76; 13,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 13,07</t>
+          <t>8,25; 12,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,59</t>
+          <t>4,64; 10,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,55</t>
+          <t>5,91; 10,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,64</t>
+          <t>5,61; 9,12</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,84; 33,31</t>
+          <t>23,31; 32,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,94; 34,17</t>
+          <t>25,82; 34,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,95; 32,28</t>
+          <t>25,84; 32,46</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,78; 44,55</t>
+          <t>33,47; 48,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,58; 51,15</t>
+          <t>34,48; 44,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,26; 47,16</t>
+          <t>35,93; 44,39</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,1; 27,59</t>
+          <t>15,97; 26,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,41; 37,09</t>
+          <t>26,7; 36,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,99; 30,82</t>
+          <t>22,89; 29,51</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,26; 19,19</t>
+          <t>11,38; 19,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,96</t>
+          <t>7,23; 12,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,83</t>
+          <t>10,07; 14,66</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,8; 35,05</t>
+          <t>27,11; 35,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,19; 30,93</t>
+          <t>27,47; 34,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,95; 31,32</t>
+          <t>28,22; 33,54</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,37</t>
+          <t>2,29; 5,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,97</t>
+          <t>4,03; 7,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,69</t>
+          <t>3,54; 5,67</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,95</t>
+          <t>16,28; 19,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,88; 20,84</t>
+          <t>17,82; 20,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,75; 18,82</t>
+          <t>17,31; 19,3</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>65002</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21499; 44264</t>
+          <t>23931; 44817</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23535; 41003</t>
+          <t>24487; 41075</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48730; 78267</t>
+          <t>52253; 79013</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37163</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67188</t>
+          <t>68224</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19303; 46628</t>
+          <t>21097; 47139</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27605; 48508</t>
+          <t>28887; 50217</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52191; 86755</t>
+          <t>52880; 86056</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82657</t>
+          <t>81650</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97311</t>
+          <t>98358</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179968</t>
+          <t>180008</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67022; 97758</t>
+          <t>68545; 96868</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84035; 110674</t>
+          <t>85242; 112430</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160216; 199276</t>
+          <t>161333; 202647</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>90493</t>
+          <t>116107</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>152628</t>
+          <t>133550</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243121</t>
+          <t>249658</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72260; 108114</t>
+          <t>95920; 138089</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86759; 205641</t>
+          <t>116156; 150571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169308; 304004</t>
+          <t>224034; 276741</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37978</t>
+          <t>40797</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64691</t>
+          <t>69879</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102668</t>
+          <t>110676</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29676; 47898</t>
+          <t>31970; 52250</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55806; 75503</t>
+          <t>59565; 81342</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90468; 116221</t>
+          <t>96921; 124926</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>24979</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63772</t>
+          <t>64876</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30081; 51236</t>
+          <t>30517; 51209</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17105; 30463</t>
+          <t>18876; 33563</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51403; 77385</t>
+          <t>53298; 77611</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>180631</t>
+          <t>208492</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>184555</t>
+          <t>223874</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>365185</t>
+          <t>432366</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>156839; 205162</t>
+          <t>182658; 235993</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83789; 254340</t>
+          <t>202444; 250718</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>224453; 440893</t>
+          <t>398111; 473147</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>44160</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68022</t>
+          <t>70853</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9589; 39925</t>
+          <t>17941; 40745</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>33071; 63370</t>
+          <t>32991; 57601</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41595; 92141</t>
+          <t>56632; 90712</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>516519</t>
+          <t>577475</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>635318</t>
+          <t>664187</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1151836</t>
+          <t>1241662</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>396623; 579041</t>
+          <t>533687; 631365</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>515132; 721511</t>
+          <t>625674; 707948</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>986434; 1258894</t>
+          <t>1175345; 1310511</t>
         </is>
       </c>
     </row>
